--- a/gstdatabase/REGISTRATION.xlsx
+++ b/gstdatabase/REGISTRATION.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Feb-26\GST Statistics Downloads 28th Feb 26\Downloads\Registration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\Registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89231BC1-7BB5-4B9C-B495-73B4747159AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581918F6-0551-460B-A001-8AE8A94E3B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -195,16 +195,125 @@
     <t>State Code</t>
   </si>
   <si>
-    <t>Maharastra</t>
-  </si>
-  <si>
     <t>Gender based analysis</t>
   </si>
   <si>
     <t>Constitution of business</t>
   </si>
   <si>
-    <t>Total no. of taxpayers registered as on last day as on 31st March 2025*</t>
+    <t>(1)</t>
+  </si>
+  <si>
+    <t>(2)</t>
+  </si>
+  <si>
+    <t>(3)</t>
+  </si>
+  <si>
+    <t>(4)</t>
+  </si>
+  <si>
+    <t>(5)</t>
+  </si>
+  <si>
+    <t>(6)</t>
+  </si>
+  <si>
+    <t>Foreign Company</t>
+  </si>
+  <si>
+    <t>Foreign Limited Liability Partnership</t>
+  </si>
+  <si>
+    <t>Hindu Undivided Family</t>
+  </si>
+  <si>
+    <t>Partnership</t>
+  </si>
+  <si>
+    <t>Proprietorship</t>
+  </si>
+  <si>
+    <t>Public Sector Undertaking</t>
+  </si>
+  <si>
+    <t>Unlimited Company</t>
+  </si>
+  <si>
+    <t>Private Limited Company</t>
+  </si>
+  <si>
+    <t>Any other body notified by committee</t>
+  </si>
+  <si>
+    <t>Limited Liability Partnership</t>
+  </si>
+  <si>
+    <t>Local Authority</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Statutory Body</t>
+  </si>
+  <si>
+    <t>Public Limited Company</t>
+  </si>
+  <si>
+    <t>Government Department</t>
+  </si>
+  <si>
+    <t>Society/ Club/ Trust/ AOP</t>
+  </si>
+  <si>
+    <t>Note -</t>
+  </si>
+  <si>
+    <t>* Total excludes temporary GSTINs</t>
+  </si>
+  <si>
+    <t># Gender of natural persons as declared in section 21 of GST registration application Form REG-01</t>
+  </si>
+  <si>
+    <t># Constitution of business which not included in summary are :
+1.	Authority or board or any other body notified by Central / State Government
+2.	Statutory Body/Government agencies
+3.	Society established by Central / State Government or Local Authority</t>
+  </si>
+  <si>
+    <t>Maharashtra</t>
+  </si>
+  <si>
+    <t>Total no. of taxpayers registered as on last day as on 31st March 2026*</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Out of (2), number and % of Taxpayers having </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">all female members </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>on 31st March 2026#</t>
+    </r>
   </si>
   <si>
     <r>
@@ -231,120 +340,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> on 31st March 2025#</t>
+      <t xml:space="preserve"> on 31st March 2026#</t>
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Out of (2), number and % of Taxpayers having </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">all female members </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>on 31st March 2025#</t>
-    </r>
-  </si>
-  <si>
-    <t>(1)</t>
-  </si>
-  <si>
-    <t>(2)</t>
-  </si>
-  <si>
-    <t>(3)</t>
-  </si>
-  <si>
-    <t>(4)</t>
-  </si>
-  <si>
-    <t>(5)</t>
-  </si>
-  <si>
-    <t>(6)</t>
-  </si>
-  <si>
-    <t>Foreign Company</t>
-  </si>
-  <si>
-    <t>Foreign Limited Liability Partnership</t>
-  </si>
-  <si>
-    <t>Hindu Undivided Family</t>
-  </si>
-  <si>
-    <t>Partnership</t>
-  </si>
-  <si>
-    <t>Proprietorship</t>
-  </si>
-  <si>
-    <t>Public Sector Undertaking</t>
-  </si>
-  <si>
-    <t>Unlimited Company</t>
-  </si>
-  <si>
-    <t>Private Limited Company</t>
-  </si>
-  <si>
-    <t>Any other body notified by committee</t>
-  </si>
-  <si>
-    <t>Limited Liability Partnership</t>
-  </si>
-  <si>
-    <t>Local Authority</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>Statutory Body</t>
-  </si>
-  <si>
-    <t>Public Limited Company</t>
-  </si>
-  <si>
-    <t>Government Department</t>
-  </si>
-  <si>
-    <t>Society/ Club/ Trust/ AOP</t>
-  </si>
-  <si>
-    <t>Note -</t>
-  </si>
-  <si>
-    <t>* Total excludes temporary GSTINs</t>
-  </si>
-  <si>
-    <t># Gender of natural persons as declared in section 21 of GST registration application Form REG-01</t>
-  </si>
-  <si>
-    <t># Constitution of business which not included in summary are :
-1.	Authority or board or any other body notified by Central / State Government
-2.	Statutory Body/Government agencies
-3.	Society established by Central / State Government or Local Authority</t>
-  </si>
-  <si>
-    <t>State Wise Registration Typewise No. of Active Tax payers as on 28th Feb 26</t>
+    <t>State Wise Registration Typewise No. of Active Tax payers as on 31st May 26</t>
   </si>
 </sst>
 </file>
@@ -356,7 +356,7 @@
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,6 +424,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -463,7 +472,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -514,19 +523,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -737,9 +733,6 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -747,33 +740,39 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -782,14 +781,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -804,9 +803,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1169,22 +1165,22 @@
         <v>24</v>
       </c>
       <c r="C3" s="6">
-        <v>144208</v>
+        <v>147601</v>
       </c>
       <c r="D3" s="6">
-        <v>8728</v>
+        <v>9197</v>
       </c>
       <c r="E3" s="6">
         <v>30</v>
       </c>
       <c r="F3" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G3" s="6">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="H3" s="6">
-        <v>8393</v>
+        <v>8440</v>
       </c>
       <c r="I3" s="6">
         <v>0</v>
@@ -1193,11 +1189,11 @@
         <v>0</v>
       </c>
       <c r="K3" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L3" s="6">
         <f>SUM(C3:J3)</f>
-        <v>161626</v>
+        <v>165547</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1208,22 +1204,22 @@
         <v>23</v>
       </c>
       <c r="C4" s="6">
-        <v>115597</v>
+        <v>117118</v>
       </c>
       <c r="D4" s="6">
-        <v>15234</v>
+        <v>15354</v>
       </c>
       <c r="E4" s="6">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F4" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G4" s="6">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="H4" s="6">
-        <v>2467</v>
+        <v>2508</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
@@ -1236,7 +1232,7 @@
       </c>
       <c r="L4" s="6">
         <f t="shared" ref="L4:L41" si="0">SUM(C4:J4)</f>
-        <v>133688</v>
+        <v>135385</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1247,25 +1243,25 @@
         <v>38</v>
       </c>
       <c r="C5" s="6">
-        <v>391164</v>
+        <v>398650</v>
       </c>
       <c r="D5" s="6">
-        <v>35503</v>
+        <v>35924</v>
       </c>
       <c r="E5" s="6">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="F5" s="6">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G5" s="6">
-        <v>702</v>
+        <v>720</v>
       </c>
       <c r="H5" s="6">
-        <v>10594</v>
+        <v>10907</v>
       </c>
       <c r="I5" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="2">
         <v>0</v>
@@ -1275,7 +1271,7 @@
       </c>
       <c r="L5" s="6">
         <f t="shared" si="0"/>
-        <v>438292</v>
+        <v>446554</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1286,22 +1282,22 @@
         <v>15</v>
       </c>
       <c r="C6" s="6">
-        <v>30069</v>
+        <v>30536</v>
       </c>
       <c r="D6" s="6">
-        <v>1538</v>
+        <v>1546</v>
       </c>
       <c r="E6" s="6">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F6" s="6">
-        <v>210</v>
+        <v>64</v>
       </c>
       <c r="G6" s="6">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="H6" s="6">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
@@ -1310,11 +1306,11 @@
         <v>0</v>
       </c>
       <c r="K6" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L6" s="6">
         <f t="shared" si="0"/>
-        <v>33245</v>
+        <v>33592</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1325,25 +1321,25 @@
         <v>45</v>
       </c>
       <c r="C7" s="6">
-        <v>188128</v>
+        <v>193023</v>
       </c>
       <c r="D7" s="6">
-        <v>29135</v>
+        <v>29593</v>
       </c>
       <c r="E7" s="6">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F7" s="6">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="G7" s="6">
-        <v>539</v>
+        <v>555</v>
       </c>
       <c r="H7" s="6">
-        <v>4541</v>
+        <v>4602</v>
       </c>
       <c r="I7" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
@@ -1353,7 +1349,7 @@
       </c>
       <c r="L7" s="6">
         <f t="shared" si="0"/>
-        <v>222435</v>
+        <v>227883</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1364,35 +1360,35 @@
         <v>22</v>
       </c>
       <c r="C8" s="6">
-        <v>596795</v>
+        <v>613701</v>
       </c>
       <c r="D8" s="6">
-        <v>13641</v>
+        <v>13773</v>
       </c>
       <c r="E8" s="6">
-        <v>2548</v>
+        <v>2657</v>
       </c>
       <c r="F8" s="6">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="G8" s="6">
-        <v>1358</v>
+        <v>1377</v>
       </c>
       <c r="H8" s="6">
-        <v>8081</v>
+        <v>8315</v>
       </c>
       <c r="I8" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L8" s="6">
         <f t="shared" si="0"/>
-        <v>622478</v>
+        <v>639845</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1403,35 +1399,35 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>856841</v>
+        <v>881693</v>
       </c>
       <c r="D9" s="6">
-        <v>15306</v>
+        <v>15559</v>
       </c>
       <c r="E9" s="6">
-        <v>3568</v>
+        <v>3707</v>
       </c>
       <c r="F9" s="6">
-        <v>194</v>
+        <v>60</v>
       </c>
       <c r="G9" s="6">
-        <v>1966</v>
+        <v>1983</v>
       </c>
       <c r="H9" s="6">
-        <v>7434</v>
+        <v>7768</v>
       </c>
       <c r="I9" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
       </c>
       <c r="K9" s="6">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L9" s="6">
         <f t="shared" si="0"/>
-        <v>885313</v>
+        <v>910777</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1442,22 +1438,22 @@
         <v>39</v>
       </c>
       <c r="C10" s="6">
-        <v>833945</v>
+        <v>856016</v>
       </c>
       <c r="D10" s="6">
-        <v>113413</v>
+        <v>113856</v>
       </c>
       <c r="E10" s="6">
-        <v>559</v>
+        <v>589</v>
       </c>
       <c r="F10" s="6">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G10" s="6">
-        <v>974</v>
+        <v>988</v>
       </c>
       <c r="H10" s="6">
-        <v>27170</v>
+        <v>27356</v>
       </c>
       <c r="I10" s="6">
         <v>0</v>
@@ -1470,7 +1466,7 @@
       </c>
       <c r="L10" s="6">
         <f t="shared" si="0"/>
-        <v>976091</v>
+        <v>998817</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1481,35 +1477,35 @@
         <v>44</v>
       </c>
       <c r="C11" s="6">
-        <v>1769877</v>
+        <v>1806964</v>
       </c>
       <c r="D11" s="6">
-        <v>288633</v>
+        <v>288291</v>
       </c>
       <c r="E11" s="6">
-        <v>1389</v>
+        <v>1458</v>
       </c>
       <c r="F11" s="6">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="G11" s="6">
-        <v>1875</v>
+        <v>1900</v>
       </c>
       <c r="H11" s="6">
-        <v>75565</v>
+        <v>77101</v>
       </c>
       <c r="I11" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
       </c>
       <c r="K11" s="6">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="0"/>
-        <v>2137377</v>
+        <v>2175735</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1520,22 +1516,22 @@
         <v>13</v>
       </c>
       <c r="C12" s="6">
-        <v>587612</v>
+        <v>609216</v>
       </c>
       <c r="D12" s="6">
-        <v>79801</v>
+        <v>80378</v>
       </c>
       <c r="E12" s="6">
         <v>103</v>
       </c>
       <c r="F12" s="6">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G12" s="6">
-        <v>611</v>
+        <v>621</v>
       </c>
       <c r="H12" s="6">
-        <v>19001</v>
+        <v>19186</v>
       </c>
       <c r="I12" s="6">
         <v>0</v>
@@ -1544,11 +1540,11 @@
         <v>0</v>
       </c>
       <c r="K12" s="6">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L12" s="6">
         <f t="shared" si="0"/>
-        <v>687136</v>
+        <v>709508</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1559,22 +1555,22 @@
         <v>40</v>
       </c>
       <c r="C13" s="6">
-        <v>10294</v>
+        <v>10428</v>
       </c>
       <c r="D13" s="6">
-        <v>678</v>
+        <v>687</v>
       </c>
       <c r="E13" s="6">
         <v>4</v>
       </c>
       <c r="F13" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G13" s="6">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="H13" s="6">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="I13" s="6">
         <v>0</v>
@@ -1587,7 +1583,7 @@
       </c>
       <c r="L13" s="6">
         <f t="shared" si="0"/>
-        <v>11665</v>
+        <v>11816</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1598,22 +1594,22 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>18256</v>
+        <v>18469</v>
       </c>
       <c r="D14" s="6">
-        <v>1865</v>
+        <v>1845</v>
       </c>
       <c r="E14" s="6">
         <v>3</v>
       </c>
       <c r="F14" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="6">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="H14" s="6">
-        <v>1654</v>
+        <v>1678</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
@@ -1626,7 +1622,7 @@
       </c>
       <c r="L14" s="6">
         <f t="shared" si="0"/>
-        <v>21923</v>
+        <v>22149</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1637,22 +1633,22 @@
         <v>34</v>
       </c>
       <c r="C15" s="6">
-        <v>8936</v>
+        <v>9205</v>
       </c>
       <c r="D15" s="6">
-        <v>1747</v>
+        <v>1742</v>
       </c>
       <c r="E15" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6">
         <v>0</v>
       </c>
       <c r="G15" s="6">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="H15" s="6">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="I15" s="6">
         <v>0</v>
@@ -1665,7 +1661,7 @@
       </c>
       <c r="L15" s="6">
         <f t="shared" si="0"/>
-        <v>11227</v>
+        <v>11502</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1676,10 +1672,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="6">
-        <v>13181</v>
+        <v>13643</v>
       </c>
       <c r="D16" s="6">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="E16" s="6">
         <v>14</v>
@@ -1688,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H16" s="6">
-        <v>719</v>
+        <v>725</v>
       </c>
       <c r="I16" s="6">
         <v>0</v>
@@ -1704,7 +1700,7 @@
       </c>
       <c r="L16" s="6">
         <f t="shared" si="0"/>
-        <v>15460</v>
+        <v>15931</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1715,22 +1711,22 @@
         <v>33</v>
       </c>
       <c r="C17" s="6">
-        <v>8824</v>
+        <v>9086</v>
       </c>
       <c r="D17" s="6">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="E17" s="6">
         <v>4</v>
       </c>
       <c r="F17" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G17" s="6">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H17" s="6">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="I17" s="6">
         <v>0</v>
@@ -1743,7 +1739,7 @@
       </c>
       <c r="L17" s="6">
         <f t="shared" si="0"/>
-        <v>9531</v>
+        <v>9815</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1754,10 +1750,10 @@
         <v>43</v>
       </c>
       <c r="C18" s="6">
-        <v>30812</v>
+        <v>31437</v>
       </c>
       <c r="D18" s="6">
-        <v>2747</v>
+        <v>2827</v>
       </c>
       <c r="E18" s="6">
         <v>11</v>
@@ -1766,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="6">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H18" s="6">
-        <v>1420</v>
+        <v>1449</v>
       </c>
       <c r="I18" s="6">
         <v>0</v>
@@ -1782,7 +1778,7 @@
       </c>
       <c r="L18" s="6">
         <f t="shared" si="0"/>
-        <v>35165</v>
+        <v>35905</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1793,22 +1789,22 @@
         <v>32</v>
       </c>
       <c r="C19" s="6">
-        <v>29408</v>
+        <v>30178</v>
       </c>
       <c r="D19" s="6">
-        <v>2038</v>
+        <v>2045</v>
       </c>
       <c r="E19" s="6">
         <v>14</v>
       </c>
       <c r="F19" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G19" s="6">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H19" s="6">
-        <v>764</v>
+        <v>786</v>
       </c>
       <c r="I19" s="6">
         <v>0</v>
@@ -1821,7 +1817,7 @@
       </c>
       <c r="L19" s="6">
         <f t="shared" si="0"/>
-        <v>32403</v>
+        <v>33204</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1832,22 +1828,22 @@
         <v>12</v>
       </c>
       <c r="C20" s="6">
-        <v>206316</v>
+        <v>210442</v>
       </c>
       <c r="D20" s="6">
-        <v>30200</v>
+        <v>30245</v>
       </c>
       <c r="E20" s="6">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F20" s="6">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G20" s="6">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="H20" s="6">
-        <v>4919</v>
+        <v>6791</v>
       </c>
       <c r="I20" s="6">
         <v>0</v>
@@ -1856,11 +1852,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="6">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L20" s="6">
         <f t="shared" si="0"/>
-        <v>241957</v>
+        <v>248006</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1871,25 +1867,25 @@
         <v>46</v>
       </c>
       <c r="C21" s="6">
-        <v>775609</v>
+        <v>790880</v>
       </c>
       <c r="D21" s="6">
-        <v>51487</v>
+        <v>51865</v>
       </c>
       <c r="E21" s="6">
-        <v>1161</v>
+        <v>1193</v>
       </c>
       <c r="F21" s="6">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="G21" s="6">
-        <v>1120</v>
+        <v>1142</v>
       </c>
       <c r="H21" s="6">
-        <v>15606</v>
+        <v>15776</v>
       </c>
       <c r="I21" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2">
         <v>0</v>
@@ -1899,7 +1895,7 @@
       </c>
       <c r="L21" s="6">
         <f t="shared" si="0"/>
-        <v>845024</v>
+        <v>860876</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1910,22 +1906,22 @@
         <v>25</v>
       </c>
       <c r="C22" s="6">
-        <v>211025</v>
+        <v>217441</v>
       </c>
       <c r="D22" s="6">
-        <v>13515</v>
+        <v>13474</v>
       </c>
       <c r="E22" s="6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F22" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G22" s="6">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="H22" s="6">
-        <v>5081</v>
+        <v>5152</v>
       </c>
       <c r="I22" s="6">
         <v>0</v>
@@ -1938,7 +1934,7 @@
       </c>
       <c r="L22" s="6">
         <f t="shared" si="0"/>
-        <v>230125</v>
+        <v>236582</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1949,22 +1945,22 @@
         <v>35</v>
       </c>
       <c r="C23" s="6">
-        <v>340390</v>
+        <v>348820</v>
       </c>
       <c r="D23" s="6">
-        <v>24378</v>
+        <v>24534</v>
       </c>
       <c r="E23" s="6">
         <v>86</v>
       </c>
       <c r="F23" s="6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G23" s="6">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="H23" s="6">
-        <v>5679</v>
+        <v>5804</v>
       </c>
       <c r="I23" s="6">
         <v>0</v>
@@ -1973,11 +1969,11 @@
         <v>0</v>
       </c>
       <c r="K23" s="6">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="L23" s="6">
         <f t="shared" si="0"/>
-        <v>370977</v>
+        <v>379696</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1988,22 +1984,22 @@
         <v>16</v>
       </c>
       <c r="C24" s="6">
-        <v>158317</v>
+        <v>160409</v>
       </c>
       <c r="D24" s="6">
-        <v>29192</v>
+        <v>29135</v>
       </c>
       <c r="E24" s="6">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F24" s="6">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="G24" s="6">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="H24" s="6">
-        <v>14359</v>
+        <v>14983</v>
       </c>
       <c r="I24" s="6">
         <v>0</v>
@@ -2012,11 +2008,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L24" s="6">
         <f t="shared" si="0"/>
-        <v>202435</v>
+        <v>205089</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2027,22 +2023,22 @@
         <v>30</v>
       </c>
       <c r="C25" s="6">
-        <v>531500</v>
+        <v>542643</v>
       </c>
       <c r="D25" s="6">
-        <v>38370</v>
+        <v>38158</v>
       </c>
       <c r="E25" s="6">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="F25" s="6">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G25" s="6">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="H25" s="6">
-        <v>26523</v>
+        <v>27151</v>
       </c>
       <c r="I25" s="6">
         <v>1</v>
@@ -2051,11 +2047,11 @@
         <v>0</v>
       </c>
       <c r="K25" s="6">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="L25" s="6">
         <f t="shared" si="0"/>
-        <v>597638</v>
+        <v>609210</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2066,22 +2062,22 @@
         <v>21</v>
       </c>
       <c r="C26" s="6">
-        <v>1252571</v>
+        <v>1283998</v>
       </c>
       <c r="D26" s="6">
-        <v>89412</v>
+        <v>89401</v>
       </c>
       <c r="E26" s="6">
-        <v>1947</v>
+        <v>2008</v>
       </c>
       <c r="F26" s="6">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G26" s="6">
-        <v>1179</v>
+        <v>1193</v>
       </c>
       <c r="H26" s="6">
-        <v>37193</v>
+        <v>38034</v>
       </c>
       <c r="I26" s="6">
         <v>3</v>
@@ -2090,11 +2086,11 @@
         <v>0</v>
       </c>
       <c r="K26" s="6">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L26" s="6">
         <f t="shared" si="0"/>
-        <v>1382342</v>
+        <v>1414671</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2144,22 +2140,22 @@
         <v>17</v>
       </c>
       <c r="C28" s="6">
-        <v>15572</v>
+        <v>15754</v>
       </c>
       <c r="D28" s="6">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E28" s="6">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F28" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G28" s="6">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="H28" s="6">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="I28" s="6">
         <v>0</v>
@@ -2172,7 +2168,7 @@
       </c>
       <c r="L28" s="6">
         <f t="shared" si="0"/>
-        <v>16791</v>
+        <v>16986</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2180,38 +2176,38 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="C29" s="6">
-        <v>1802727</v>
+        <v>1851690</v>
       </c>
       <c r="D29" s="6">
-        <v>116731</v>
+        <v>117145</v>
       </c>
       <c r="E29" s="6">
-        <v>7513</v>
+        <v>7776</v>
       </c>
       <c r="F29" s="6">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="G29" s="6">
-        <v>1975</v>
+        <v>2022</v>
       </c>
       <c r="H29" s="6">
-        <v>54005</v>
+        <v>54473</v>
       </c>
       <c r="I29" s="6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
       </c>
       <c r="K29" s="6">
-        <v>329</v>
+        <v>269</v>
       </c>
       <c r="L29" s="6">
         <f t="shared" si="0"/>
-        <v>1983096</v>
+        <v>2033190</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2222,35 +2218,35 @@
         <v>26</v>
       </c>
       <c r="C30" s="6">
-        <v>976165</v>
+        <v>988228</v>
       </c>
       <c r="D30" s="6">
-        <v>95031</v>
+        <v>96444</v>
       </c>
       <c r="E30" s="6">
-        <v>2272</v>
+        <v>2368</v>
       </c>
       <c r="F30" s="6">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G30" s="6">
-        <v>1872</v>
+        <v>1911</v>
       </c>
       <c r="H30" s="6">
-        <v>23382</v>
+        <v>24117</v>
       </c>
       <c r="I30" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
       <c r="K30" s="6">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="L30" s="6">
         <f t="shared" si="0"/>
-        <v>1098897</v>
+        <v>1113245</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2261,22 +2257,22 @@
         <v>20</v>
       </c>
       <c r="C31" s="6">
-        <v>42404</v>
+        <v>43155</v>
       </c>
       <c r="D31" s="6">
-        <v>5250</v>
+        <v>5350</v>
       </c>
       <c r="E31" s="6">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="F31" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G31" s="6">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="H31" s="6">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="I31" s="6">
         <v>0</v>
@@ -2289,7 +2285,7 @@
       </c>
       <c r="L31" s="6">
         <f t="shared" si="0"/>
-        <v>49127</v>
+        <v>50001</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2300,7 +2296,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="2">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="D32" s="2">
         <v>24</v>
@@ -2312,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="H32" s="2">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
@@ -2328,7 +2324,7 @@
       </c>
       <c r="L32" s="6">
         <f t="shared" si="0"/>
-        <v>507</v>
+        <v>532</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2339,25 +2335,25 @@
         <v>27</v>
       </c>
       <c r="C33" s="6">
-        <v>378672</v>
+        <v>382885</v>
       </c>
       <c r="D33" s="6">
-        <v>50567</v>
+        <v>51431</v>
       </c>
       <c r="E33" s="6">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="F33" s="6">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="G33" s="6">
-        <v>1032</v>
+        <v>1057</v>
       </c>
       <c r="H33" s="6">
-        <v>10252</v>
+        <v>10435</v>
       </c>
       <c r="I33" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -2367,7 +2363,7 @@
       </c>
       <c r="L33" s="6">
         <f t="shared" si="0"/>
-        <v>441006</v>
+        <v>446276</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2378,35 +2374,35 @@
         <v>41</v>
       </c>
       <c r="C34" s="6">
-        <v>1140452</v>
+        <v>1157550</v>
       </c>
       <c r="D34" s="6">
-        <v>61283</v>
+        <v>62704</v>
       </c>
       <c r="E34" s="6">
-        <v>1699</v>
+        <v>1769</v>
       </c>
       <c r="F34" s="6">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G34" s="6">
-        <v>1636</v>
+        <v>1658</v>
       </c>
       <c r="H34" s="6">
-        <v>23942</v>
+        <v>24397</v>
       </c>
       <c r="I34" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2">
         <v>0</v>
       </c>
       <c r="K34" s="6">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="L34" s="6">
         <f t="shared" si="0"/>
-        <v>1229088</v>
+        <v>1248141</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2417,22 +2413,22 @@
         <v>37</v>
       </c>
       <c r="C35" s="6">
-        <v>23090</v>
+        <v>23477</v>
       </c>
       <c r="D35" s="6">
-        <v>2127</v>
+        <v>2208</v>
       </c>
       <c r="E35" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F35" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G35" s="6">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="H35" s="6">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="I35" s="6">
         <v>0</v>
@@ -2445,7 +2441,7 @@
       </c>
       <c r="L35" s="6">
         <f t="shared" si="0"/>
-        <v>25961</v>
+        <v>26440</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2456,22 +2452,22 @@
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>5258</v>
+        <v>5494</v>
       </c>
       <c r="D36" s="6">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="E36" s="6">
         <v>6</v>
       </c>
       <c r="F36" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G36" s="6">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="I36" s="6">
         <v>0</v>
@@ -2484,7 +2480,7 @@
       </c>
       <c r="L36" s="6">
         <f t="shared" si="0"/>
-        <v>6475</v>
+        <v>6740</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2495,22 +2491,22 @@
         <v>42</v>
       </c>
       <c r="C37" s="6">
-        <v>494393</v>
+        <v>505737</v>
       </c>
       <c r="D37" s="6">
-        <v>47267</v>
+        <v>47340</v>
       </c>
       <c r="E37" s="6">
-        <v>1000</v>
+        <v>1037</v>
       </c>
       <c r="F37" s="6">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G37" s="6">
-        <v>740</v>
+        <v>703</v>
       </c>
       <c r="H37" s="6">
-        <v>22190</v>
+        <v>20688</v>
       </c>
       <c r="I37" s="6">
         <v>4</v>
@@ -2519,11 +2515,11 @@
         <v>0</v>
       </c>
       <c r="K37" s="6">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L37" s="6">
         <f t="shared" si="0"/>
-        <v>565700</v>
+        <v>575616</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2534,22 +2530,22 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>358266</v>
+        <v>365498</v>
       </c>
       <c r="D38" s="6">
-        <v>80930</v>
+        <v>81543</v>
       </c>
       <c r="E38" s="6">
         <v>141</v>
       </c>
       <c r="F38" s="6">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G38" s="6">
-        <v>716</v>
+        <v>734</v>
       </c>
       <c r="H38" s="6">
-        <v>7145</v>
+        <v>7287</v>
       </c>
       <c r="I38" s="6">
         <v>1</v>
@@ -2558,11 +2554,11 @@
         <v>0</v>
       </c>
       <c r="K38" s="6">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L38" s="6">
         <f t="shared" si="0"/>
-        <v>447246</v>
+        <v>455239</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2573,10 +2569,10 @@
         <v>28</v>
       </c>
       <c r="C39" s="6">
-        <v>9008</v>
+        <v>9274</v>
       </c>
       <c r="D39" s="6">
-        <v>639</v>
+        <v>660</v>
       </c>
       <c r="E39" s="6">
         <v>1</v>
@@ -2585,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="G39" s="6">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="H39" s="6">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="I39" s="6">
         <v>0</v>
@@ -2601,7 +2597,7 @@
       </c>
       <c r="L39" s="6">
         <f t="shared" si="0"/>
-        <v>10429</v>
+        <v>10724</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2612,7 +2608,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
@@ -2640,7 +2636,7 @@
       </c>
       <c r="L40" s="6">
         <f t="shared" si="0"/>
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2672,62 +2668,62 @@
         <v>0</v>
       </c>
       <c r="J41" s="2">
-        <v>855</v>
+        <v>902</v>
       </c>
       <c r="K41" s="2">
         <v>0</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>902</v>
       </c>
     </row>
     <row r="42" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="9"/>
-      <c r="B42" s="8" t="s">
+      <c r="A42" s="8"/>
+      <c r="B42" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="23">
         <f>SUM(C3:C41)</f>
-        <v>14356103</v>
-      </c>
-      <c r="D42" s="7">
-        <f t="shared" ref="D42:L42" si="1">SUM(D3:D41)</f>
-        <v>1349260</v>
-      </c>
-      <c r="E42" s="7">
+        <v>14680775</v>
+      </c>
+      <c r="D42" s="23">
+        <f t="shared" ref="D42:J42" si="1">SUM(D3:D41)</f>
+        <v>1357156</v>
+      </c>
+      <c r="E42" s="23">
         <f t="shared" si="1"/>
-        <v>25878</v>
-      </c>
-      <c r="F42" s="7">
+        <v>26846</v>
+      </c>
+      <c r="F42" s="23">
         <f t="shared" si="1"/>
-        <v>1391</v>
-      </c>
-      <c r="G42" s="7">
+        <v>889</v>
+      </c>
+      <c r="G42" s="23">
         <f t="shared" si="1"/>
-        <v>23934</v>
-      </c>
-      <c r="H42" s="7">
+        <v>24365</v>
+      </c>
+      <c r="H42" s="23">
         <f t="shared" si="1"/>
-        <v>423360</v>
-      </c>
-      <c r="I42" s="7">
+        <v>431247</v>
+      </c>
+      <c r="I42" s="23">
+        <f>SUM(I3:I41)</f>
+        <v>45</v>
+      </c>
+      <c r="J42" s="23">
         <f t="shared" si="1"/>
-        <v>51</v>
-      </c>
-      <c r="J42" s="7">
-        <f t="shared" si="1"/>
-        <v>855</v>
-      </c>
-      <c r="K42" s="7">
-        <f t="shared" si="1"/>
-        <v>2413</v>
-      </c>
-      <c r="L42" s="7">
+        <v>902</v>
+      </c>
+      <c r="K42" s="23">
+        <f>SUM(K3:K41)</f>
+        <v>2367</v>
+      </c>
+      <c r="L42" s="23">
         <f>SUM(L3:L41)</f>
-        <v>16180832</v>
-      </c>
-      <c r="M42" s="10"/>
+        <v>16522225</v>
+      </c>
+      <c r="M42" s="9"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:L42">
@@ -2748,8 +2744,7 @@
   <cols>
     <col min="3" max="3" width="54.5546875" customWidth="1"/>
     <col min="4" max="4" width="24.88671875" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" customWidth="1"/>
+    <col min="5" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="16.88671875" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
@@ -2757,7 +2752,7 @@
     <row r="1" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C2" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D2" s="27"/>
       <c r="E2" s="27"/>
@@ -2765,437 +2760,400 @@
       <c r="G2" s="27"/>
       <c r="H2" s="28"/>
     </row>
-    <row r="3" spans="3:8" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="C3" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>54</v>
+    <row r="3" spans="3:8" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>80</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="F3" s="29"/>
       <c r="G3" s="29" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="30"/>
+    </row>
+    <row r="4" spans="3:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C4" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="H3" s="30"/>
-    </row>
-    <row r="4" spans="3:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C4" s="16" t="s">
+      <c r="G4" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="H4" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="12" t="s">
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="D5" s="12">
+        <v>1949</v>
+      </c>
+      <c r="E5" s="12">
+        <v>241</v>
+      </c>
+      <c r="F5" s="13">
+        <v>0.12365315546434069</v>
+      </c>
+      <c r="G5" s="12">
+        <v>44</v>
+      </c>
+      <c r="H5" s="18">
+        <v>2.2575679835813236E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C6" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="D6" s="12">
+        <v>158</v>
+      </c>
+      <c r="E6" s="12">
+        <v>84</v>
+      </c>
+      <c r="F6" s="13">
+        <v>0.53164556962025311</v>
+      </c>
+      <c r="G6" s="12">
+        <v>9</v>
+      </c>
+      <c r="H6" s="18">
+        <v>5.6962025316455694E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C7" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="D7" s="12">
+        <v>91220</v>
+      </c>
+      <c r="E7" s="12">
+        <v>4346</v>
+      </c>
+      <c r="F7" s="13">
+        <v>4.7643060732295552E-2</v>
+      </c>
+      <c r="G7" s="12">
+        <v>477</v>
+      </c>
+      <c r="H7" s="18">
+        <v>5.2291164218373166E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C8" s="17" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C5" s="18" t="s">
+      <c r="D8" s="12">
+        <v>1559421</v>
+      </c>
+      <c r="E8" s="12">
+        <v>697880</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0.44752507501181527</v>
+      </c>
+      <c r="G8" s="12">
+        <v>82284</v>
+      </c>
+      <c r="H8" s="18">
+        <v>5.2765738052777282E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="13">
-        <v>1886</v>
-      </c>
-      <c r="E5" s="13">
-        <v>205</v>
-      </c>
-      <c r="F5" s="14">
-        <f>E5/D5</f>
-        <v>0.10869565217391304</v>
-      </c>
-      <c r="G5" s="13">
-        <v>48</v>
-      </c>
-      <c r="H5" s="19">
-        <f>G5/D5</f>
-        <v>2.5450689289501591E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C6" s="18" t="s">
+      <c r="D9" s="12">
+        <v>12585263</v>
+      </c>
+      <c r="E9" s="12">
+        <v>2342159</v>
+      </c>
+      <c r="F9" s="13">
+        <v>0.18610330193338034</v>
+      </c>
+      <c r="G9" s="12">
+        <v>2341994</v>
+      </c>
+      <c r="H9" s="18">
+        <v>0.18609019136111815</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="13">
-        <v>144</v>
-      </c>
-      <c r="E6" s="13">
+      <c r="D10" s="12">
+        <v>6925</v>
+      </c>
+      <c r="E10" s="12">
+        <v>1128</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0.16288808664259927</v>
+      </c>
+      <c r="G10" s="12">
+        <v>116</v>
+      </c>
+      <c r="H10" s="18">
+        <v>1.6750902527075812E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="12">
+        <v>129</v>
+      </c>
+      <c r="E11" s="12">
         <v>64</v>
       </c>
-      <c r="F6" s="14">
-        <f>E6/D6</f>
-        <v>0.44444444444444442</v>
-      </c>
-      <c r="G6" s="13">
-        <v>10</v>
-      </c>
-      <c r="H6" s="19">
-        <f t="shared" ref="H6:H21" si="0">G6/D6</f>
-        <v>6.9444444444444448E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C7" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="13">
-        <v>86040</v>
-      </c>
-      <c r="E7" s="13">
-        <v>3637</v>
-      </c>
-      <c r="F7" s="14">
-        <f t="shared" ref="F7:F21" si="1">E7/D7</f>
-        <v>4.2271036727103674E-2</v>
-      </c>
-      <c r="G7" s="13">
-        <v>457</v>
-      </c>
-      <c r="H7" s="19">
-        <f t="shared" si="0"/>
-        <v>5.3114830311483032E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C8" s="18" t="s">
+      <c r="F11" s="13">
+        <v>0.49612403100775193</v>
+      </c>
+      <c r="G11" s="12">
+        <v>7</v>
+      </c>
+      <c r="H11" s="18">
+        <v>5.4263565891472867E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="13">
-        <v>1470847</v>
-      </c>
-      <c r="E8" s="13">
-        <v>615955</v>
-      </c>
-      <c r="F8" s="14">
-        <f t="shared" si="1"/>
-        <v>0.41877571222567678</v>
-      </c>
-      <c r="G8" s="13">
-        <v>78450</v>
-      </c>
-      <c r="H8" s="19">
-        <f t="shared" si="0"/>
-        <v>5.3336614889244086E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C9" s="18" t="s">
+      <c r="D12" s="12">
+        <v>1162506</v>
+      </c>
+      <c r="E12" s="12">
+        <v>587216</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0.50512943589108361</v>
+      </c>
+      <c r="G12" s="12">
+        <v>55668</v>
+      </c>
+      <c r="H12" s="18">
+        <v>4.7886204458299567E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="13">
-        <v>11719409</v>
-      </c>
-      <c r="E9" s="13">
-        <v>1959367</v>
-      </c>
-      <c r="F9" s="14">
-        <f t="shared" si="1"/>
-        <v>0.16718991546416717</v>
-      </c>
-      <c r="G9" s="13">
-        <v>1959307</v>
-      </c>
-      <c r="H9" s="19">
-        <f t="shared" si="0"/>
-        <v>0.16718479575207248</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C10" s="18" t="s">
+      <c r="D13" s="12">
+        <v>9802</v>
+      </c>
+      <c r="E13" s="12">
+        <v>8</v>
+      </c>
+      <c r="F13" s="13">
+        <v>8.1615996735360131E-4</v>
+      </c>
+      <c r="G13" s="12">
+        <v>5</v>
+      </c>
+      <c r="H13" s="18">
+        <v>5.1009997959600086E-4</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C14" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="D10" s="13">
-        <v>6278</v>
-      </c>
-      <c r="E10" s="13">
-        <v>899</v>
-      </c>
-      <c r="F10" s="14">
-        <f t="shared" si="1"/>
-        <v>0.14319847085058937</v>
-      </c>
-      <c r="G10" s="13">
-        <v>135</v>
-      </c>
-      <c r="H10" s="19">
-        <f t="shared" si="0"/>
-        <v>2.150366358712966E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C11" s="18" t="s">
+      <c r="D14" s="12">
+        <v>215950</v>
+      </c>
+      <c r="E14" s="12">
+        <v>114010</v>
+      </c>
+      <c r="F14" s="13">
+        <v>0.52794628386200504</v>
+      </c>
+      <c r="G14" s="12">
+        <v>15668</v>
+      </c>
+      <c r="H14" s="18">
+        <v>7.2553831905533689E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C15" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="13">
-        <v>128</v>
-      </c>
-      <c r="E11" s="13">
-        <v>54</v>
-      </c>
-      <c r="F11" s="14">
-        <f t="shared" si="1"/>
-        <v>0.421875</v>
-      </c>
-      <c r="G11" s="13">
-        <v>6</v>
-      </c>
-      <c r="H11" s="19">
-        <f t="shared" si="0"/>
-        <v>4.6875E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C12" s="18" t="s">
+      <c r="D15" s="12">
+        <v>120062</v>
+      </c>
+      <c r="E15" s="12">
+        <v>1333</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1.1102596991554364E-2</v>
+      </c>
+      <c r="G15" s="12">
+        <v>1001</v>
+      </c>
+      <c r="H15" s="18">
+        <v>8.337359031167231E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C16" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="D12" s="13">
-        <v>1019642</v>
-      </c>
-      <c r="E12" s="13">
-        <v>477002</v>
-      </c>
-      <c r="F12" s="14">
-        <f t="shared" si="1"/>
-        <v>0.4678132128727534</v>
-      </c>
-      <c r="G12" s="13">
-        <v>51225</v>
-      </c>
-      <c r="H12" s="19">
-        <f t="shared" si="0"/>
-        <v>5.0238220865754843E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C13" s="18" t="s">
+      <c r="D16" s="12">
+        <v>112769</v>
+      </c>
+      <c r="E16" s="12">
+        <v>12047</v>
+      </c>
+      <c r="F16" s="13">
+        <v>0.10682900442497495</v>
+      </c>
+      <c r="G16" s="12">
+        <v>9572</v>
+      </c>
+      <c r="H16" s="18">
+        <v>8.4881483386391648E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C17" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="13">
-        <v>10006</v>
-      </c>
-      <c r="E13" s="13">
-        <v>9</v>
-      </c>
-      <c r="F13" s="14">
-        <f t="shared" si="1"/>
-        <v>8.9946032380571654E-4</v>
-      </c>
-      <c r="G13" s="13">
-        <v>6</v>
-      </c>
-      <c r="H13" s="19">
-        <f t="shared" si="0"/>
-        <v>5.9964021587047766E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C14" s="18" t="s">
+      <c r="D17" s="12">
+        <v>4804</v>
+      </c>
+      <c r="E17" s="12">
+        <v>143</v>
+      </c>
+      <c r="F17" s="13">
+        <v>2.9766860949208992E-2</v>
+      </c>
+      <c r="G17" s="12">
+        <v>77</v>
+      </c>
+      <c r="H17" s="18">
+        <v>1.6028309741881765E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C18" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="13">
-        <v>168206</v>
-      </c>
-      <c r="E14" s="13">
-        <v>81061</v>
-      </c>
-      <c r="F14" s="14">
-        <f t="shared" si="1"/>
-        <v>0.48191503275745218</v>
-      </c>
-      <c r="G14" s="13">
-        <v>12407</v>
-      </c>
-      <c r="H14" s="19">
-        <f t="shared" si="0"/>
-        <v>7.3760745752232376E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C15" s="18" t="s">
+      <c r="D18" s="12">
+        <v>94100</v>
+      </c>
+      <c r="E18" s="12">
+        <v>44208</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0.46979808714133903</v>
+      </c>
+      <c r="G18" s="12">
+        <v>1080</v>
+      </c>
+      <c r="H18" s="18">
+        <v>1.1477151965993623E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C19" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="13">
-        <v>104279</v>
-      </c>
-      <c r="E15" s="13">
-        <v>1294</v>
-      </c>
-      <c r="F15" s="14">
-        <f t="shared" si="1"/>
-        <v>1.2409018114864929E-2</v>
-      </c>
-      <c r="G15" s="13">
-        <v>1031</v>
-      </c>
-      <c r="H15" s="19">
-        <f t="shared" si="0"/>
-        <v>9.8869379261404509E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C16" s="18" t="s">
+      <c r="D19" s="12">
+        <v>218214</v>
+      </c>
+      <c r="E19" s="12">
+        <v>1399</v>
+      </c>
+      <c r="F19" s="13">
+        <v>6.4111376905239808E-3</v>
+      </c>
+      <c r="G19" s="12">
+        <v>1055</v>
+      </c>
+      <c r="H19" s="18">
+        <v>4.8347035478933523E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C20" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="13">
-        <v>85067</v>
-      </c>
-      <c r="E16" s="13">
-        <v>8337</v>
-      </c>
-      <c r="F16" s="14">
-        <f t="shared" si="1"/>
-        <v>9.8005101860886124E-2</v>
-      </c>
-      <c r="G16" s="13">
-        <v>6504</v>
-      </c>
-      <c r="H16" s="19">
-        <f t="shared" si="0"/>
-        <v>7.6457380652897131E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C17" s="18" t="s">
+      <c r="D20" s="12">
+        <v>156658</v>
+      </c>
+      <c r="E20" s="12">
+        <v>38548</v>
+      </c>
+      <c r="F20" s="13">
+        <v>0.2460646759182423</v>
+      </c>
+      <c r="G20" s="12">
+        <v>13301</v>
+      </c>
+      <c r="H20" s="18">
+        <v>8.4904696855570727E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="19">
+        <v>16339930</v>
+      </c>
+      <c r="E21" s="19">
+        <v>3844814</v>
+      </c>
+      <c r="F21" s="20">
+        <v>0.23530174241872517</v>
+      </c>
+      <c r="G21" s="19">
+        <v>2522358</v>
+      </c>
+      <c r="H21" s="21">
+        <v>0.15436773596949313</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C23" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="13">
-        <v>4802</v>
-      </c>
-      <c r="E17" s="13">
-        <v>126</v>
-      </c>
-      <c r="F17" s="14">
-        <f t="shared" si="1"/>
-        <v>2.6239067055393587E-2</v>
-      </c>
-      <c r="G17" s="13">
-        <v>75</v>
-      </c>
-      <c r="H17" s="19">
-        <f t="shared" si="0"/>
-        <v>1.5618492294877134E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C18" s="18" t="s">
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C24" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="D18" s="13">
-        <v>86306</v>
-      </c>
-      <c r="E18" s="13">
-        <v>37720</v>
-      </c>
-      <c r="F18" s="14">
-        <f t="shared" si="1"/>
-        <v>0.43704956781683774</v>
-      </c>
-      <c r="G18" s="13">
-        <v>1246</v>
-      </c>
-      <c r="H18" s="19">
-        <f t="shared" si="0"/>
-        <v>1.4437003221097026E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C19" s="18" t="s">
+    </row>
+    <row r="25" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="14" t="s">
         <v>77</v>
-      </c>
-      <c r="D19" s="13">
-        <v>196337</v>
-      </c>
-      <c r="E19" s="13">
-        <v>1269</v>
-      </c>
-      <c r="F19" s="14">
-        <f t="shared" si="1"/>
-        <v>6.4633767450862547E-3</v>
-      </c>
-      <c r="G19" s="13">
-        <v>1013</v>
-      </c>
-      <c r="H19" s="19">
-        <f t="shared" si="0"/>
-        <v>5.1594961723974595E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C20" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="13">
-        <v>143689</v>
-      </c>
-      <c r="E20" s="13">
-        <v>31221</v>
-      </c>
-      <c r="F20" s="14">
-        <f t="shared" si="1"/>
-        <v>0.2172817682634022</v>
-      </c>
-      <c r="G20" s="13">
-        <v>12441</v>
-      </c>
-      <c r="H20" s="19">
-        <f t="shared" si="0"/>
-        <v>8.6582828191441238E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="21">
-        <f>SUM(D5:D20)</f>
-        <v>15103066</v>
-      </c>
-      <c r="E21" s="21">
-        <f t="shared" ref="E21:G21" si="2">SUM(E5:E20)</f>
-        <v>3218220</v>
-      </c>
-      <c r="F21" s="22">
-        <f t="shared" si="1"/>
-        <v>0.21308388641087841</v>
-      </c>
-      <c r="G21" s="21">
-        <f t="shared" si="2"/>
-        <v>2124361</v>
-      </c>
-      <c r="H21" s="23">
-        <f t="shared" si="0"/>
-        <v>0.14065759892726418</v>
-      </c>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C23" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C24" s="15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="15" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="26" spans="3:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="31" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D26" s="32"/>
     </row>

--- a/gstdatabase/REGISTRATION.xlsx
+++ b/gstdatabase/REGISTRATION.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\May-26\GST Statistics Downloads 31st May 26\Downloads\Registration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\Registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{581918F6-0551-460B-A001-8AE8A94E3B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B72E22-3423-40BE-9F08-5723AEC4C6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -344,7 +344,7 @@
     </r>
   </si>
   <si>
-    <t>State Wise Registration Typewise No. of Active Tax payers as on 31st May 26</t>
+    <t>State Wise Registration Typewise No. of Active Tax payers as on 30th Jun 26</t>
   </si>
 </sst>
 </file>
@@ -1165,22 +1165,22 @@
         <v>24</v>
       </c>
       <c r="C3" s="6">
-        <v>147601</v>
+        <v>149857</v>
       </c>
       <c r="D3" s="6">
-        <v>9197</v>
+        <v>9217</v>
       </c>
       <c r="E3" s="6">
         <v>30</v>
       </c>
       <c r="F3" s="6">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G3" s="6">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H3" s="6">
-        <v>8440</v>
+        <v>8449</v>
       </c>
       <c r="I3" s="6">
         <v>0</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="L3" s="6">
         <f>SUM(C3:J3)</f>
-        <v>165547</v>
+        <v>167830</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1204,10 +1204,10 @@
         <v>23</v>
       </c>
       <c r="C4" s="6">
-        <v>117118</v>
+        <v>118429</v>
       </c>
       <c r="D4" s="6">
-        <v>15354</v>
+        <v>15313</v>
       </c>
       <c r="E4" s="6">
         <v>63</v>
@@ -1216,10 +1216,10 @@
         <v>4</v>
       </c>
       <c r="G4" s="6">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H4" s="6">
-        <v>2508</v>
+        <v>2515</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
@@ -1228,11 +1228,11 @@
         <v>0</v>
       </c>
       <c r="K4" s="6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L4" s="6">
         <f t="shared" ref="L4:L41" si="0">SUM(C4:J4)</f>
-        <v>135385</v>
+        <v>136660</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1243,25 +1243,25 @@
         <v>38</v>
       </c>
       <c r="C5" s="6">
-        <v>398650</v>
+        <v>402779</v>
       </c>
       <c r="D5" s="6">
-        <v>35924</v>
+        <v>35964</v>
       </c>
       <c r="E5" s="6">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F5" s="6">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="G5" s="6">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="H5" s="6">
-        <v>10907</v>
+        <v>10987</v>
       </c>
       <c r="I5" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
         <v>0</v>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="L5" s="6">
         <f t="shared" si="0"/>
-        <v>446554</v>
+        <v>450789</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1282,22 +1282,22 @@
         <v>15</v>
       </c>
       <c r="C6" s="6">
-        <v>30536</v>
+        <v>30768</v>
       </c>
       <c r="D6" s="6">
-        <v>1546</v>
+        <v>1550</v>
       </c>
       <c r="E6" s="6">
         <v>168</v>
       </c>
       <c r="F6" s="6">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="G6" s="6">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H6" s="6">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="L6" s="6">
         <f t="shared" si="0"/>
-        <v>33592</v>
+        <v>33812</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1321,22 +1321,22 @@
         <v>45</v>
       </c>
       <c r="C7" s="6">
-        <v>193023</v>
+        <v>195938</v>
       </c>
       <c r="D7" s="6">
-        <v>29593</v>
+        <v>29575</v>
       </c>
       <c r="E7" s="6">
         <v>92</v>
       </c>
       <c r="F7" s="6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" s="6">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="H7" s="6">
-        <v>4602</v>
+        <v>4625</v>
       </c>
       <c r="I7" s="6">
         <v>3</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="L7" s="6">
         <f t="shared" si="0"/>
-        <v>227883</v>
+        <v>230806</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1360,22 +1360,22 @@
         <v>22</v>
       </c>
       <c r="C8" s="6">
-        <v>613701</v>
+        <v>623152</v>
       </c>
       <c r="D8" s="6">
-        <v>13773</v>
+        <v>13752</v>
       </c>
       <c r="E8" s="6">
-        <v>2657</v>
+        <v>2677</v>
       </c>
       <c r="F8" s="6">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="G8" s="6">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="H8" s="6">
-        <v>8315</v>
+        <v>8381</v>
       </c>
       <c r="I8" s="6">
         <v>3</v>
@@ -1384,11 +1384,11 @@
         <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L8" s="6">
         <f t="shared" si="0"/>
-        <v>639845</v>
+        <v>649360</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1399,35 +1399,35 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>881693</v>
+        <v>892909</v>
       </c>
       <c r="D9" s="6">
-        <v>15559</v>
+        <v>15520</v>
       </c>
       <c r="E9" s="6">
-        <v>3707</v>
+        <v>3749</v>
       </c>
       <c r="F9" s="6">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="G9" s="6">
-        <v>1983</v>
+        <v>1992</v>
       </c>
       <c r="H9" s="6">
-        <v>7768</v>
+        <v>7868</v>
       </c>
       <c r="I9" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
       </c>
       <c r="K9" s="6">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L9" s="6">
         <f t="shared" si="0"/>
-        <v>910777</v>
+        <v>922133</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1438,22 +1438,22 @@
         <v>39</v>
       </c>
       <c r="C10" s="6">
-        <v>856016</v>
+        <v>869570</v>
       </c>
       <c r="D10" s="6">
-        <v>113856</v>
+        <v>113304</v>
       </c>
       <c r="E10" s="6">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F10" s="6">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G10" s="6">
-        <v>988</v>
+        <v>1000</v>
       </c>
       <c r="H10" s="6">
-        <v>27356</v>
+        <v>27509</v>
       </c>
       <c r="I10" s="6">
         <v>0</v>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L10" s="6">
         <f t="shared" si="0"/>
-        <v>998817</v>
+        <v>1011997</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1477,22 +1477,22 @@
         <v>44</v>
       </c>
       <c r="C11" s="6">
-        <v>1806964</v>
+        <v>1831715</v>
       </c>
       <c r="D11" s="6">
-        <v>288291</v>
+        <v>287744</v>
       </c>
       <c r="E11" s="6">
-        <v>1458</v>
+        <v>1479</v>
       </c>
       <c r="F11" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G11" s="6">
-        <v>1900</v>
+        <v>1910</v>
       </c>
       <c r="H11" s="6">
-        <v>77101</v>
+        <v>77576</v>
       </c>
       <c r="I11" s="6">
         <v>2</v>
@@ -1501,11 +1501,11 @@
         <v>0</v>
       </c>
       <c r="K11" s="6">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="0"/>
-        <v>2175735</v>
+        <v>2200442</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1516,10 +1516,10 @@
         <v>13</v>
       </c>
       <c r="C12" s="6">
-        <v>609216</v>
+        <v>620481</v>
       </c>
       <c r="D12" s="6">
-        <v>80378</v>
+        <v>80162</v>
       </c>
       <c r="E12" s="6">
         <v>103</v>
@@ -1528,10 +1528,10 @@
         <v>4</v>
       </c>
       <c r="G12" s="6">
-        <v>621</v>
+        <v>626</v>
       </c>
       <c r="H12" s="6">
-        <v>19186</v>
+        <v>19219</v>
       </c>
       <c r="I12" s="6">
         <v>0</v>
@@ -1540,11 +1540,11 @@
         <v>0</v>
       </c>
       <c r="K12" s="6">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L12" s="6">
         <f t="shared" si="0"/>
-        <v>709508</v>
+        <v>720595</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1555,22 +1555,22 @@
         <v>40</v>
       </c>
       <c r="C13" s="6">
-        <v>10428</v>
+        <v>10508</v>
       </c>
       <c r="D13" s="6">
-        <v>687</v>
+        <v>680</v>
       </c>
       <c r="E13" s="6">
         <v>4</v>
       </c>
       <c r="F13" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13" s="6">
         <v>155</v>
       </c>
       <c r="H13" s="6">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="I13" s="6">
         <v>0</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="L13" s="6">
         <f t="shared" si="0"/>
-        <v>11816</v>
+        <v>11889</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1594,10 +1594,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>18469</v>
+        <v>18771</v>
       </c>
       <c r="D14" s="6">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="E14" s="6">
         <v>3</v>
@@ -1606,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="6">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H14" s="6">
-        <v>1678</v>
+        <v>1682</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
@@ -1622,7 +1622,7 @@
       </c>
       <c r="L14" s="6">
         <f t="shared" si="0"/>
-        <v>22149</v>
+        <v>22457</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1633,10 +1633,10 @@
         <v>34</v>
       </c>
       <c r="C15" s="6">
-        <v>9205</v>
+        <v>9299</v>
       </c>
       <c r="D15" s="6">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="E15" s="6">
         <v>3</v>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="L15" s="6">
         <f t="shared" si="0"/>
-        <v>11502</v>
+        <v>11599</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1672,10 +1672,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="6">
-        <v>13643</v>
+        <v>13949</v>
       </c>
       <c r="D16" s="6">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="E16" s="6">
         <v>14</v>
@@ -1687,7 +1687,7 @@
         <v>173</v>
       </c>
       <c r="H16" s="6">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="I16" s="6">
         <v>0</v>
@@ -1696,11 +1696,11 @@
         <v>0</v>
       </c>
       <c r="K16" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L16" s="6">
         <f t="shared" si="0"/>
-        <v>15931</v>
+        <v>16241</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1711,7 +1711,7 @@
         <v>33</v>
       </c>
       <c r="C17" s="6">
-        <v>9086</v>
+        <v>9196</v>
       </c>
       <c r="D17" s="6">
         <v>204</v>
@@ -1720,13 +1720,13 @@
         <v>4</v>
       </c>
       <c r="F17" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H17" s="6">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="I17" s="6">
         <v>0</v>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="L17" s="6">
         <f t="shared" si="0"/>
-        <v>9815</v>
+        <v>9927</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1750,10 +1750,10 @@
         <v>43</v>
       </c>
       <c r="C18" s="6">
-        <v>31437</v>
+        <v>31775</v>
       </c>
       <c r="D18" s="6">
-        <v>2827</v>
+        <v>2813</v>
       </c>
       <c r="E18" s="6">
         <v>11</v>
@@ -1762,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="G18" s="6">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H18" s="6">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="I18" s="6">
         <v>0</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="L18" s="6">
         <f t="shared" si="0"/>
-        <v>35905</v>
+        <v>36233</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1789,10 +1789,10 @@
         <v>32</v>
       </c>
       <c r="C19" s="6">
-        <v>30178</v>
+        <v>31016</v>
       </c>
       <c r="D19" s="6">
-        <v>2045</v>
+        <v>2039</v>
       </c>
       <c r="E19" s="6">
         <v>14</v>
@@ -1801,10 +1801,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="6">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H19" s="6">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="I19" s="6">
         <v>0</v>
@@ -1817,7 +1817,7 @@
       </c>
       <c r="L19" s="6">
         <f t="shared" si="0"/>
-        <v>33204</v>
+        <v>34045</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1828,22 +1828,22 @@
         <v>12</v>
       </c>
       <c r="C20" s="6">
-        <v>210442</v>
+        <v>214801</v>
       </c>
       <c r="D20" s="6">
-        <v>30245</v>
+        <v>30144</v>
       </c>
       <c r="E20" s="6">
         <v>77</v>
       </c>
       <c r="F20" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G20" s="6">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="H20" s="6">
-        <v>6791</v>
+        <v>7291</v>
       </c>
       <c r="I20" s="6">
         <v>0</v>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="L20" s="6">
         <f t="shared" si="0"/>
-        <v>248006</v>
+        <v>252772</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1867,22 +1867,22 @@
         <v>46</v>
       </c>
       <c r="C21" s="6">
-        <v>790880</v>
+        <v>801311</v>
       </c>
       <c r="D21" s="6">
-        <v>51865</v>
+        <v>51731</v>
       </c>
       <c r="E21" s="6">
-        <v>1193</v>
+        <v>1205</v>
       </c>
       <c r="F21" s="6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G21" s="6">
-        <v>1142</v>
+        <v>1151</v>
       </c>
       <c r="H21" s="6">
-        <v>15776</v>
+        <v>15838</v>
       </c>
       <c r="I21" s="6">
         <v>1</v>
@@ -1891,11 +1891,11 @@
         <v>0</v>
       </c>
       <c r="K21" s="6">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L21" s="6">
         <f t="shared" si="0"/>
-        <v>860876</v>
+        <v>871261</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1906,22 +1906,22 @@
         <v>25</v>
       </c>
       <c r="C22" s="6">
-        <v>217441</v>
+        <v>220892</v>
       </c>
       <c r="D22" s="6">
-        <v>13474</v>
+        <v>13097</v>
       </c>
       <c r="E22" s="6">
         <v>63</v>
       </c>
       <c r="F22" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G22" s="6">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="H22" s="6">
-        <v>5152</v>
+        <v>5176</v>
       </c>
       <c r="I22" s="6">
         <v>0</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="L22" s="6">
         <f t="shared" si="0"/>
-        <v>236582</v>
+        <v>239687</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1945,22 +1945,22 @@
         <v>35</v>
       </c>
       <c r="C23" s="6">
-        <v>348820</v>
+        <v>353374</v>
       </c>
       <c r="D23" s="6">
-        <v>24534</v>
+        <v>24500</v>
       </c>
       <c r="E23" s="6">
         <v>86</v>
       </c>
       <c r="F23" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="6">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="H23" s="6">
-        <v>5804</v>
+        <v>5850</v>
       </c>
       <c r="I23" s="6">
         <v>0</v>
@@ -1969,11 +1969,11 @@
         <v>0</v>
       </c>
       <c r="K23" s="6">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L23" s="6">
         <f t="shared" si="0"/>
-        <v>379696</v>
+        <v>384264</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1984,22 +1984,22 @@
         <v>16</v>
       </c>
       <c r="C24" s="6">
-        <v>160409</v>
+        <v>162226</v>
       </c>
       <c r="D24" s="6">
-        <v>29135</v>
+        <v>29363</v>
       </c>
       <c r="E24" s="6">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F24" s="6">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G24" s="6">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H24" s="6">
-        <v>14983</v>
+        <v>15032</v>
       </c>
       <c r="I24" s="6">
         <v>0</v>
@@ -2008,11 +2008,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="6">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L24" s="6">
         <f t="shared" si="0"/>
-        <v>205089</v>
+        <v>207194</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2023,22 +2023,22 @@
         <v>30</v>
       </c>
       <c r="C25" s="6">
-        <v>542643</v>
+        <v>549998</v>
       </c>
       <c r="D25" s="6">
-        <v>38158</v>
+        <v>38129</v>
       </c>
       <c r="E25" s="6">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F25" s="6">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G25" s="6">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="H25" s="6">
-        <v>27151</v>
+        <v>27226</v>
       </c>
       <c r="I25" s="6">
         <v>1</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="L25" s="6">
         <f t="shared" si="0"/>
-        <v>609210</v>
+        <v>616636</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2062,35 +2062,35 @@
         <v>21</v>
       </c>
       <c r="C26" s="6">
-        <v>1283998</v>
+        <v>1301405</v>
       </c>
       <c r="D26" s="6">
-        <v>89401</v>
+        <v>89422</v>
       </c>
       <c r="E26" s="6">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="F26" s="6">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="G26" s="6">
-        <v>1193</v>
+        <v>1203</v>
       </c>
       <c r="H26" s="6">
-        <v>38034</v>
+        <v>38304</v>
       </c>
       <c r="I26" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J26" s="2">
         <v>0</v>
       </c>
       <c r="K26" s="6">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="L26" s="6">
         <f t="shared" si="0"/>
-        <v>1414671</v>
+        <v>1432420</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2140,13 +2140,13 @@
         <v>17</v>
       </c>
       <c r="C28" s="6">
-        <v>15754</v>
+        <v>15863</v>
       </c>
       <c r="D28" s="6">
         <v>569</v>
       </c>
       <c r="E28" s="6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F28" s="6">
         <v>1</v>
@@ -2155,7 +2155,7 @@
         <v>223</v>
       </c>
       <c r="H28" s="6">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I28" s="6">
         <v>0</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L28" s="6">
         <f t="shared" si="0"/>
-        <v>16986</v>
+        <v>17095</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2179,22 +2179,22 @@
         <v>79</v>
       </c>
       <c r="C29" s="6">
-        <v>1851690</v>
+        <v>1876545</v>
       </c>
       <c r="D29" s="6">
-        <v>117145</v>
+        <v>117274</v>
       </c>
       <c r="E29" s="6">
-        <v>7776</v>
+        <v>7863</v>
       </c>
       <c r="F29" s="6">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G29" s="6">
-        <v>2022</v>
+        <v>2032</v>
       </c>
       <c r="H29" s="6">
-        <v>54473</v>
+        <v>54563</v>
       </c>
       <c r="I29" s="6">
         <v>11</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="L29" s="6">
         <f t="shared" si="0"/>
-        <v>2033190</v>
+        <v>2058362</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2218,25 +2218,25 @@
         <v>26</v>
       </c>
       <c r="C30" s="6">
-        <v>988228</v>
+        <v>998160</v>
       </c>
       <c r="D30" s="6">
-        <v>96444</v>
+        <v>96667</v>
       </c>
       <c r="E30" s="6">
-        <v>2368</v>
+        <v>2406</v>
       </c>
       <c r="F30" s="6">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="G30" s="6">
-        <v>1911</v>
+        <v>1920</v>
       </c>
       <c r="H30" s="6">
-        <v>24117</v>
+        <v>24265</v>
       </c>
       <c r="I30" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="L30" s="6">
         <f t="shared" si="0"/>
-        <v>1113245</v>
+        <v>1123567</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2257,22 +2257,22 @@
         <v>20</v>
       </c>
       <c r="C31" s="6">
-        <v>43155</v>
+        <v>43638</v>
       </c>
       <c r="D31" s="6">
-        <v>5350</v>
+        <v>5365</v>
       </c>
       <c r="E31" s="6">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F31" s="6">
         <v>10</v>
       </c>
       <c r="G31" s="6">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H31" s="6">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="I31" s="6">
         <v>0</v>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="L31" s="6">
         <f t="shared" si="0"/>
-        <v>50001</v>
+        <v>50505</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2296,7 +2296,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D32" s="2">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>101</v>
       </c>
       <c r="H32" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="L32" s="6">
         <f t="shared" si="0"/>
-        <v>532</v>
+        <v>535</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2335,25 +2335,25 @@
         <v>27</v>
       </c>
       <c r="C33" s="6">
-        <v>382885</v>
+        <v>386062</v>
       </c>
       <c r="D33" s="6">
-        <v>51431</v>
+        <v>51529</v>
       </c>
       <c r="E33" s="6">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F33" s="6">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="G33" s="6">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="H33" s="6">
-        <v>10435</v>
+        <v>10460</v>
       </c>
       <c r="I33" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="L33" s="6">
         <f t="shared" si="0"/>
-        <v>446276</v>
+        <v>449594</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2374,35 +2374,35 @@
         <v>41</v>
       </c>
       <c r="C34" s="6">
-        <v>1157550</v>
+        <v>1165871</v>
       </c>
       <c r="D34" s="6">
-        <v>62704</v>
+        <v>62634</v>
       </c>
       <c r="E34" s="6">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="F34" s="6">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="G34" s="6">
-        <v>1658</v>
+        <v>1668</v>
       </c>
       <c r="H34" s="6">
-        <v>24397</v>
+        <v>24520</v>
       </c>
       <c r="I34" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J34" s="2">
         <v>0</v>
       </c>
       <c r="K34" s="6">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L34" s="6">
         <f t="shared" si="0"/>
-        <v>1248141</v>
+        <v>1256552</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2413,19 +2413,19 @@
         <v>37</v>
       </c>
       <c r="C35" s="6">
-        <v>23477</v>
+        <v>23680</v>
       </c>
       <c r="D35" s="6">
-        <v>2208</v>
+        <v>2154</v>
       </c>
       <c r="E35" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F35" s="6">
         <v>1</v>
       </c>
       <c r="G35" s="6">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H35" s="6">
         <v>488</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="L35" s="6">
         <f t="shared" si="0"/>
-        <v>26440</v>
+        <v>26587</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2452,10 +2452,10 @@
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>5494</v>
+        <v>5599</v>
       </c>
       <c r="D36" s="6">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="E36" s="6">
         <v>6</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="L36" s="6">
         <f t="shared" si="0"/>
-        <v>6740</v>
+        <v>6839</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2491,35 +2491,35 @@
         <v>42</v>
       </c>
       <c r="C37" s="6">
-        <v>505737</v>
+        <v>511263</v>
       </c>
       <c r="D37" s="6">
-        <v>47340</v>
+        <v>47248</v>
       </c>
       <c r="E37" s="6">
-        <v>1037</v>
+        <v>1051</v>
       </c>
       <c r="F37" s="6">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="G37" s="6">
-        <v>703</v>
+        <v>692</v>
       </c>
       <c r="H37" s="6">
-        <v>20688</v>
+        <v>20198</v>
       </c>
       <c r="I37" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
       </c>
       <c r="K37" s="6">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L37" s="6">
         <f t="shared" si="0"/>
-        <v>575616</v>
+        <v>580604</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2530,35 +2530,35 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>365498</v>
+        <v>369701</v>
       </c>
       <c r="D38" s="6">
-        <v>81543</v>
+        <v>81140</v>
       </c>
       <c r="E38" s="6">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="G38" s="6">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="H38" s="6">
-        <v>7287</v>
+        <v>7334</v>
       </c>
       <c r="I38" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" s="2">
         <v>0</v>
       </c>
       <c r="K38" s="6">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L38" s="6">
         <f t="shared" si="0"/>
-        <v>455239</v>
+        <v>459107</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2569,10 +2569,10 @@
         <v>28</v>
       </c>
       <c r="C39" s="6">
-        <v>9274</v>
+        <v>9397</v>
       </c>
       <c r="D39" s="6">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="E39" s="6">
         <v>1</v>
@@ -2584,7 +2584,7 @@
         <v>87</v>
       </c>
       <c r="H39" s="6">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="I39" s="6">
         <v>0</v>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="L39" s="6">
         <f t="shared" si="0"/>
-        <v>10724</v>
+        <v>10851</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2668,14 +2668,14 @@
         <v>0</v>
       </c>
       <c r="J41" s="2">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="K41" s="2">
         <v>0</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="0"/>
-        <v>902</v>
+        <v>917</v>
       </c>
     </row>
     <row r="42" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
@@ -2685,43 +2685,43 @@
       </c>
       <c r="C42" s="23">
         <f>SUM(C3:C41)</f>
-        <v>14680775</v>
+        <v>14870332</v>
       </c>
       <c r="D42" s="23">
         <f t="shared" ref="D42:J42" si="1">SUM(D3:D41)</f>
-        <v>1357156</v>
+        <v>1355180</v>
       </c>
       <c r="E42" s="23">
         <f t="shared" si="1"/>
-        <v>26846</v>
+        <v>27115</v>
       </c>
       <c r="F42" s="23">
         <f t="shared" si="1"/>
-        <v>889</v>
+        <v>982</v>
       </c>
       <c r="G42" s="23">
         <f t="shared" si="1"/>
-        <v>24365</v>
+        <v>24494</v>
       </c>
       <c r="H42" s="23">
         <f t="shared" si="1"/>
-        <v>431247</v>
+        <v>433198</v>
       </c>
       <c r="I42" s="23">
         <f>SUM(I3:I41)</f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J42" s="23">
         <f t="shared" si="1"/>
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="K42" s="23">
         <f>SUM(K3:K41)</f>
-        <v>2367</v>
+        <v>2384</v>
       </c>
       <c r="L42" s="23">
         <f>SUM(L3:L41)</f>
-        <v>16522225</v>
+        <v>16712262</v>
       </c>
       <c r="M42" s="9"/>
     </row>

--- a/gstdatabase/REGISTRATION.xlsx
+++ b/gstdatabase/REGISTRATION.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jun-26\GST Statistics Downloads 31st May 26\Downloads\Registration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infosystechnologies-my.sharepoint.com/personal/sai_enjeti_ad_infosys_com/Documents/Documents/GST Statistics Downloads 31st Jul 26/GST Statistics Downloads 31st Jul 26/Downloads/Registration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2B72E22-3423-40BE-9F08-5723AEC4C6A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{61065DE5-6E1C-4A06-A4DF-5BE4D49607A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EB75211-BDA8-493B-AAF9-8F78D7C0D0AB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="Gender based analysis" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$2:$L$41</definedName>
@@ -344,7 +344,7 @@
     </r>
   </si>
   <si>
-    <t>State Wise Registration Typewise No. of Active Tax payers as on 30th Jun 26</t>
+    <t>State Wise Registration Typewise No. of Active Tax payers as on 31st Jul 26</t>
   </si>
 </sst>
 </file>
@@ -352,9 +352,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -713,7 +713,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -746,8 +746,8 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -756,14 +756,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1087,23 +1087,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" style="3" customWidth="1"/>
-    <col min="3" max="5" width="16.44140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.6328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" style="3" customWidth="1"/>
+    <col min="3" max="5" width="16.453125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.90625" style="3" customWidth="1"/>
     <col min="7" max="7" width="18" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14.44140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.6640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="16.44140625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.33203125" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="3"/>
+    <col min="8" max="8" width="17.6328125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14.453125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9.6328125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.453125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.453125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.36328125" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9.08984375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>83</v>
       </c>
@@ -1119,7 +1119,7 @@
       <c r="K1" s="25"/>
       <c r="L1" s="25"/>
     </row>
-    <row r="2" spans="1:12" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>50</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1165,22 +1165,22 @@
         <v>24</v>
       </c>
       <c r="C3" s="6">
-        <v>149857</v>
+        <v>152446</v>
       </c>
       <c r="D3" s="6">
-        <v>9217</v>
+        <v>9183</v>
       </c>
       <c r="E3" s="6">
         <v>30</v>
       </c>
       <c r="F3" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G3" s="6">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H3" s="6">
-        <v>8449</v>
+        <v>8424</v>
       </c>
       <c r="I3" s="6">
         <v>0</v>
@@ -1189,14 +1189,14 @@
         <v>0</v>
       </c>
       <c r="K3" s="6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L3" s="6">
         <f>SUM(C3:J3)</f>
-        <v>167830</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>170362</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1204,22 +1204,22 @@
         <v>23</v>
       </c>
       <c r="C4" s="6">
-        <v>118429</v>
+        <v>119499</v>
       </c>
       <c r="D4" s="6">
-        <v>15313</v>
+        <v>15188</v>
       </c>
       <c r="E4" s="6">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F4" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G4" s="6">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H4" s="6">
-        <v>2515</v>
+        <v>2533</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
@@ -1228,14 +1228,14 @@
         <v>0</v>
       </c>
       <c r="K4" s="6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L4" s="6">
         <f t="shared" ref="L4:L41" si="0">SUM(C4:J4)</f>
-        <v>136660</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>137624</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1243,22 +1243,22 @@
         <v>38</v>
       </c>
       <c r="C5" s="6">
-        <v>402779</v>
+        <v>405536</v>
       </c>
       <c r="D5" s="6">
-        <v>35964</v>
+        <v>35854</v>
       </c>
       <c r="E5" s="6">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="F5" s="6">
-        <v>38</v>
+        <v>99</v>
       </c>
       <c r="G5" s="6">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="H5" s="6">
-        <v>10987</v>
+        <v>11077</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
@@ -1271,10 +1271,10 @@
       </c>
       <c r="L5" s="6">
         <f t="shared" si="0"/>
-        <v>450789</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>453594</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1282,22 +1282,22 @@
         <v>15</v>
       </c>
       <c r="C6" s="6">
-        <v>30768</v>
+        <v>30969</v>
       </c>
       <c r="D6" s="6">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="E6" s="6">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F6" s="6">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="G6" s="6">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="H6" s="6">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
@@ -1310,10 +1310,10 @@
       </c>
       <c r="L6" s="6">
         <f t="shared" si="0"/>
-        <v>33812</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>34030</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1321,38 +1321,38 @@
         <v>45</v>
       </c>
       <c r="C7" s="6">
-        <v>195938</v>
+        <v>197647</v>
       </c>
       <c r="D7" s="6">
-        <v>29575</v>
+        <v>29401</v>
       </c>
       <c r="E7" s="6">
         <v>92</v>
       </c>
       <c r="F7" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" s="6">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="H7" s="6">
-        <v>4625</v>
+        <v>4658</v>
       </c>
       <c r="I7" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
       </c>
       <c r="K7" s="6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="6">
         <f t="shared" si="0"/>
-        <v>230806</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>232381</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1360,38 +1360,38 @@
         <v>22</v>
       </c>
       <c r="C8" s="6">
-        <v>623152</v>
+        <v>629112</v>
       </c>
       <c r="D8" s="6">
-        <v>13752</v>
+        <v>13661</v>
       </c>
       <c r="E8" s="6">
-        <v>2677</v>
+        <v>2705</v>
       </c>
       <c r="F8" s="6">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="G8" s="6">
-        <v>1387</v>
+        <v>1393</v>
       </c>
       <c r="H8" s="6">
-        <v>8381</v>
+        <v>8463</v>
       </c>
       <c r="I8" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L8" s="6">
         <f t="shared" si="0"/>
-        <v>649360</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>655358</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1399,25 +1399,25 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>892909</v>
+        <v>900961</v>
       </c>
       <c r="D9" s="6">
-        <v>15520</v>
+        <v>15418</v>
       </c>
       <c r="E9" s="6">
-        <v>3749</v>
+        <v>3777</v>
       </c>
       <c r="F9" s="6">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="G9" s="6">
-        <v>1992</v>
+        <v>1998</v>
       </c>
       <c r="H9" s="6">
-        <v>7868</v>
+        <v>7931</v>
       </c>
       <c r="I9" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
@@ -1427,10 +1427,10 @@
       </c>
       <c r="L9" s="6">
         <f t="shared" si="0"/>
-        <v>922133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>930215</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1438,22 +1438,22 @@
         <v>39</v>
       </c>
       <c r="C10" s="6">
-        <v>869570</v>
+        <v>852027</v>
       </c>
       <c r="D10" s="6">
-        <v>113304</v>
+        <v>112035</v>
       </c>
       <c r="E10" s="6">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="F10" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G10" s="6">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="H10" s="6">
-        <v>27509</v>
+        <v>27720</v>
       </c>
       <c r="I10" s="6">
         <v>0</v>
@@ -1466,10 +1466,10 @@
       </c>
       <c r="L10" s="6">
         <f t="shared" si="0"/>
-        <v>1011997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>993412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1477,38 +1477,38 @@
         <v>44</v>
       </c>
       <c r="C11" s="6">
-        <v>1831715</v>
+        <v>1848771</v>
       </c>
       <c r="D11" s="6">
-        <v>287744</v>
+        <v>283999</v>
       </c>
       <c r="E11" s="6">
-        <v>1479</v>
+        <v>1484</v>
       </c>
       <c r="F11" s="6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G11" s="6">
-        <v>1910</v>
+        <v>1914</v>
       </c>
       <c r="H11" s="6">
-        <v>77576</v>
+        <v>78016</v>
       </c>
       <c r="I11" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" s="2">
         <v>0</v>
       </c>
       <c r="K11" s="6">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="0"/>
-        <v>2200442</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2214203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1516,22 +1516,22 @@
         <v>13</v>
       </c>
       <c r="C12" s="6">
-        <v>620481</v>
+        <v>630014</v>
       </c>
       <c r="D12" s="6">
-        <v>80162</v>
+        <v>78804</v>
       </c>
       <c r="E12" s="6">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F12" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G12" s="6">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="H12" s="6">
-        <v>19219</v>
+        <v>19277</v>
       </c>
       <c r="I12" s="6">
         <v>0</v>
@@ -1540,14 +1540,14 @@
         <v>0</v>
       </c>
       <c r="K12" s="6">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L12" s="6">
         <f t="shared" si="0"/>
-        <v>720595</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>728838</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1555,10 +1555,10 @@
         <v>40</v>
       </c>
       <c r="C13" s="6">
-        <v>10508</v>
+        <v>10572</v>
       </c>
       <c r="D13" s="6">
-        <v>680</v>
+        <v>665</v>
       </c>
       <c r="E13" s="6">
         <v>4</v>
@@ -1567,7 +1567,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="6">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H13" s="6">
         <v>541</v>
@@ -1583,10 +1583,10 @@
       </c>
       <c r="L13" s="6">
         <f t="shared" si="0"/>
-        <v>11889</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11940</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1594,10 +1594,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>18771</v>
+        <v>19026</v>
       </c>
       <c r="D14" s="6">
-        <v>1846</v>
+        <v>1833</v>
       </c>
       <c r="E14" s="6">
         <v>3</v>
@@ -1606,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="6">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H14" s="6">
-        <v>1682</v>
+        <v>1687</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
@@ -1622,10 +1622,10 @@
       </c>
       <c r="L14" s="6">
         <f t="shared" si="0"/>
-        <v>22457</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>22706</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1633,10 +1633,10 @@
         <v>34</v>
       </c>
       <c r="C15" s="6">
-        <v>9299</v>
+        <v>9413</v>
       </c>
       <c r="D15" s="6">
-        <v>1745</v>
+        <v>1730</v>
       </c>
       <c r="E15" s="6">
         <v>3</v>
@@ -1645,10 +1645,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="6">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H15" s="6">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="I15" s="6">
         <v>0</v>
@@ -1661,10 +1661,10 @@
       </c>
       <c r="L15" s="6">
         <f t="shared" si="0"/>
-        <v>11599</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11703</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1672,10 +1672,10 @@
         <v>31</v>
       </c>
       <c r="C16" s="6">
-        <v>13949</v>
+        <v>14263</v>
       </c>
       <c r="D16" s="6">
-        <v>1377</v>
+        <v>1363</v>
       </c>
       <c r="E16" s="6">
         <v>14</v>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H16" s="6">
         <v>728</v>
@@ -1700,10 +1700,10 @@
       </c>
       <c r="L16" s="6">
         <f t="shared" si="0"/>
-        <v>16241</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>16542</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1711,10 +1711,10 @@
         <v>33</v>
       </c>
       <c r="C17" s="6">
-        <v>9196</v>
+        <v>9359</v>
       </c>
       <c r="D17" s="6">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="E17" s="6">
         <v>4</v>
@@ -1723,10 +1723,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="6">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H17" s="6">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="I17" s="6">
         <v>0</v>
@@ -1739,10 +1739,10 @@
       </c>
       <c r="L17" s="6">
         <f t="shared" si="0"/>
-        <v>9927</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10075</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1750,10 +1750,10 @@
         <v>43</v>
       </c>
       <c r="C18" s="6">
-        <v>31775</v>
+        <v>32071</v>
       </c>
       <c r="D18" s="6">
-        <v>2813</v>
+        <v>2805</v>
       </c>
       <c r="E18" s="6">
         <v>11</v>
@@ -1762,7 +1762,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="6">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H18" s="6">
         <v>1452</v>
@@ -1778,10 +1778,10 @@
       </c>
       <c r="L18" s="6">
         <f t="shared" si="0"/>
-        <v>36233</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>36523</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1789,10 +1789,10 @@
         <v>32</v>
       </c>
       <c r="C19" s="6">
-        <v>31016</v>
+        <v>31455</v>
       </c>
       <c r="D19" s="6">
-        <v>2039</v>
+        <v>2017</v>
       </c>
       <c r="E19" s="6">
         <v>14</v>
@@ -1801,10 +1801,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="6">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H19" s="6">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="I19" s="6">
         <v>0</v>
@@ -1817,10 +1817,10 @@
       </c>
       <c r="L19" s="6">
         <f t="shared" si="0"/>
-        <v>34045</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>34465</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1828,22 +1828,22 @@
         <v>12</v>
       </c>
       <c r="C20" s="6">
-        <v>214801</v>
+        <v>218664</v>
       </c>
       <c r="D20" s="6">
-        <v>30144</v>
+        <v>29920</v>
       </c>
       <c r="E20" s="6">
         <v>77</v>
       </c>
       <c r="F20" s="6">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G20" s="6">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="H20" s="6">
-        <v>7291</v>
+        <v>7846</v>
       </c>
       <c r="I20" s="6">
         <v>0</v>
@@ -1852,14 +1852,14 @@
         <v>0</v>
       </c>
       <c r="K20" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L20" s="6">
         <f t="shared" si="0"/>
-        <v>252772</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>256975</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1867,25 +1867,25 @@
         <v>46</v>
       </c>
       <c r="C21" s="6">
-        <v>801311</v>
+        <v>811072</v>
       </c>
       <c r="D21" s="6">
-        <v>51731</v>
+        <v>51383</v>
       </c>
       <c r="E21" s="6">
-        <v>1205</v>
+        <v>1220</v>
       </c>
       <c r="F21" s="6">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G21" s="6">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="H21" s="6">
-        <v>15838</v>
+        <v>15900</v>
       </c>
       <c r="I21" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J21" s="2">
         <v>0</v>
@@ -1895,10 +1895,10 @@
       </c>
       <c r="L21" s="6">
         <f t="shared" si="0"/>
-        <v>871261</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>880771</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1906,22 +1906,22 @@
         <v>25</v>
       </c>
       <c r="C22" s="6">
-        <v>220892</v>
+        <v>223169</v>
       </c>
       <c r="D22" s="6">
-        <v>13097</v>
+        <v>13033</v>
       </c>
       <c r="E22" s="6">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F22" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G22" s="6">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H22" s="6">
-        <v>5176</v>
+        <v>5198</v>
       </c>
       <c r="I22" s="6">
         <v>0</v>
@@ -1930,14 +1930,14 @@
         <v>0</v>
       </c>
       <c r="K22" s="6">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L22" s="6">
         <f t="shared" si="0"/>
-        <v>239687</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>241923</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1945,10 +1945,10 @@
         <v>35</v>
       </c>
       <c r="C23" s="6">
-        <v>353374</v>
+        <v>356638</v>
       </c>
       <c r="D23" s="6">
-        <v>24500</v>
+        <v>24303</v>
       </c>
       <c r="E23" s="6">
         <v>86</v>
@@ -1957,10 +1957,10 @@
         <v>6</v>
       </c>
       <c r="G23" s="6">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H23" s="6">
-        <v>5850</v>
+        <v>5903</v>
       </c>
       <c r="I23" s="6">
         <v>0</v>
@@ -1969,14 +1969,14 @@
         <v>0</v>
       </c>
       <c r="K23" s="6">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L23" s="6">
         <f t="shared" si="0"/>
-        <v>384264</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>387386</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1984,22 +1984,22 @@
         <v>16</v>
       </c>
       <c r="C24" s="6">
-        <v>162226</v>
+        <v>163631</v>
       </c>
       <c r="D24" s="6">
-        <v>29363</v>
+        <v>29541</v>
       </c>
       <c r="E24" s="6">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="G24" s="6">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H24" s="6">
-        <v>15032</v>
+        <v>15102</v>
       </c>
       <c r="I24" s="6">
         <v>0</v>
@@ -2012,10 +2012,10 @@
       </c>
       <c r="L24" s="6">
         <f t="shared" si="0"/>
-        <v>207194</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>208881</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2023,38 +2023,38 @@
         <v>30</v>
       </c>
       <c r="C25" s="6">
-        <v>549998</v>
+        <v>554370</v>
       </c>
       <c r="D25" s="6">
-        <v>38129</v>
+        <v>37884</v>
       </c>
       <c r="E25" s="6">
         <v>364</v>
       </c>
       <c r="F25" s="6">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="G25" s="6">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="H25" s="6">
-        <v>27226</v>
+        <v>27304</v>
       </c>
       <c r="I25" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2">
         <v>0</v>
       </c>
       <c r="K25" s="6">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="L25" s="6">
         <f t="shared" si="0"/>
-        <v>616636</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>620858</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2062,22 +2062,22 @@
         <v>21</v>
       </c>
       <c r="C26" s="6">
-        <v>1301405</v>
+        <v>1312143</v>
       </c>
       <c r="D26" s="6">
-        <v>89422</v>
+        <v>88821</v>
       </c>
       <c r="E26" s="6">
-        <v>2015</v>
+        <v>2028</v>
       </c>
       <c r="F26" s="6">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G26" s="6">
-        <v>1203</v>
+        <v>1211</v>
       </c>
       <c r="H26" s="6">
-        <v>38304</v>
+        <v>38598</v>
       </c>
       <c r="I26" s="6">
         <v>4</v>
@@ -2086,14 +2086,14 @@
         <v>0</v>
       </c>
       <c r="K26" s="6">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L26" s="6">
         <f t="shared" si="0"/>
-        <v>1432420</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1442869</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2140,22 +2140,22 @@
         <v>17</v>
       </c>
       <c r="C28" s="6">
-        <v>15863</v>
+        <v>15918</v>
       </c>
       <c r="D28" s="6">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="E28" s="6">
         <v>28</v>
       </c>
       <c r="F28" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="6">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H28" s="6">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="I28" s="6">
         <v>0</v>
@@ -2168,10 +2168,10 @@
       </c>
       <c r="L28" s="6">
         <f t="shared" si="0"/>
-        <v>17095</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -2179,25 +2179,25 @@
         <v>79</v>
       </c>
       <c r="C29" s="6">
-        <v>1876545</v>
+        <v>1892625</v>
       </c>
       <c r="D29" s="6">
-        <v>117274</v>
+        <v>116664</v>
       </c>
       <c r="E29" s="6">
-        <v>7863</v>
+        <v>7923</v>
       </c>
       <c r="F29" s="6">
-        <v>74</v>
+        <v>178</v>
       </c>
       <c r="G29" s="6">
-        <v>2032</v>
+        <v>2036</v>
       </c>
       <c r="H29" s="6">
-        <v>54563</v>
+        <v>54642</v>
       </c>
       <c r="I29" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
@@ -2207,10 +2207,10 @@
       </c>
       <c r="L29" s="6">
         <f t="shared" si="0"/>
-        <v>2058362</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>2074080</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2218,38 +2218,38 @@
         <v>26</v>
       </c>
       <c r="C30" s="6">
-        <v>998160</v>
+        <v>1005922</v>
       </c>
       <c r="D30" s="6">
-        <v>96667</v>
+        <v>96195</v>
       </c>
       <c r="E30" s="6">
-        <v>2406</v>
+        <v>2431</v>
       </c>
       <c r="F30" s="6">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="G30" s="6">
-        <v>1920</v>
+        <v>1928</v>
       </c>
       <c r="H30" s="6">
-        <v>24265</v>
+        <v>24368</v>
       </c>
       <c r="I30" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
       <c r="K30" s="6">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L30" s="6">
         <f t="shared" si="0"/>
-        <v>1123567</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1131004</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2257,22 +2257,22 @@
         <v>20</v>
       </c>
       <c r="C31" s="6">
-        <v>43638</v>
+        <v>44009</v>
       </c>
       <c r="D31" s="6">
-        <v>5365</v>
+        <v>5343</v>
       </c>
       <c r="E31" s="6">
         <v>149</v>
       </c>
       <c r="F31" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G31" s="6">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="H31" s="6">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="I31" s="6">
         <v>0</v>
@@ -2285,10 +2285,10 @@
       </c>
       <c r="L31" s="6">
         <f t="shared" si="0"/>
-        <v>50505</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>50861</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>29</v>
       </c>
       <c r="C32" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="D32" s="2">
         <v>24</v>
@@ -2308,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H32" s="2">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
@@ -2324,10 +2324,10 @@
       </c>
       <c r="L32" s="6">
         <f t="shared" si="0"/>
-        <v>535</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2335,25 +2335,25 @@
         <v>27</v>
       </c>
       <c r="C33" s="6">
-        <v>386062</v>
+        <v>389392</v>
       </c>
       <c r="D33" s="6">
-        <v>51529</v>
+        <v>51398</v>
       </c>
       <c r="E33" s="6">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F33" s="6">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="G33" s="6">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="H33" s="6">
-        <v>10460</v>
+        <v>10498</v>
       </c>
       <c r="I33" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -2363,10 +2363,10 @@
       </c>
       <c r="L33" s="6">
         <f t="shared" si="0"/>
-        <v>449594</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>452855</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2374,38 +2374,38 @@
         <v>41</v>
       </c>
       <c r="C34" s="6">
-        <v>1165871</v>
+        <v>1173931</v>
       </c>
       <c r="D34" s="6">
-        <v>62634</v>
+        <v>62071</v>
       </c>
       <c r="E34" s="6">
-        <v>1777</v>
+        <v>1784</v>
       </c>
       <c r="F34" s="6">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="G34" s="6">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="H34" s="6">
-        <v>24520</v>
+        <v>24599</v>
       </c>
       <c r="I34" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34" s="2">
         <v>0</v>
       </c>
       <c r="K34" s="6">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L34" s="6">
         <f t="shared" si="0"/>
-        <v>1256552</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>1264150</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2413,13 +2413,13 @@
         <v>37</v>
       </c>
       <c r="C35" s="6">
-        <v>23680</v>
+        <v>23932</v>
       </c>
       <c r="D35" s="6">
         <v>2154</v>
       </c>
       <c r="E35" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F35" s="6">
         <v>1</v>
@@ -2428,7 +2428,7 @@
         <v>235</v>
       </c>
       <c r="H35" s="6">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="I35" s="6">
         <v>0</v>
@@ -2441,10 +2441,10 @@
       </c>
       <c r="L35" s="6">
         <f t="shared" si="0"/>
-        <v>26587</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>26841</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2452,10 +2452,10 @@
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>5599</v>
+        <v>5696</v>
       </c>
       <c r="D36" s="6">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="E36" s="6">
         <v>6</v>
@@ -2464,10 +2464,10 @@
         <v>0</v>
       </c>
       <c r="G36" s="6">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H36" s="6">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I36" s="6">
         <v>0</v>
@@ -2480,10 +2480,10 @@
       </c>
       <c r="L36" s="6">
         <f t="shared" si="0"/>
-        <v>6839</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6941</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2491,38 +2491,38 @@
         <v>42</v>
       </c>
       <c r="C37" s="6">
-        <v>511263</v>
+        <v>515683</v>
       </c>
       <c r="D37" s="6">
-        <v>47248</v>
+        <v>46912</v>
       </c>
       <c r="E37" s="6">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="F37" s="6">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="G37" s="6">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="H37" s="6">
-        <v>20198</v>
+        <v>19731</v>
       </c>
       <c r="I37" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
       </c>
       <c r="K37" s="6">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L37" s="6">
         <f t="shared" si="0"/>
-        <v>580604</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>584202</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2530,22 +2530,22 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>369701</v>
+        <v>372981</v>
       </c>
       <c r="D38" s="6">
-        <v>81140</v>
+        <v>80400</v>
       </c>
       <c r="E38" s="6">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F38" s="6">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G38" s="6">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="H38" s="6">
-        <v>7334</v>
+        <v>7602</v>
       </c>
       <c r="I38" s="6">
         <v>0</v>
@@ -2558,10 +2558,10 @@
       </c>
       <c r="L38" s="6">
         <f t="shared" si="0"/>
-        <v>459107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>461920</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2569,22 +2569,22 @@
         <v>28</v>
       </c>
       <c r="C39" s="6">
-        <v>9397</v>
+        <v>9521</v>
       </c>
       <c r="D39" s="6">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="E39" s="6">
         <v>1</v>
       </c>
       <c r="F39" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" s="6">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H39" s="6">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="I39" s="6">
         <v>0</v>
@@ -2597,10 +2597,10 @@
       </c>
       <c r="L39" s="6">
         <f t="shared" si="0"/>
-        <v>10851</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>10982</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>97</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>99</v>
       </c>
@@ -2668,60 +2668,60 @@
         <v>0</v>
       </c>
       <c r="J41" s="2">
-        <v>917</v>
+        <v>948</v>
       </c>
       <c r="K41" s="2">
         <v>0</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="0"/>
-        <v>917</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="8"/>
       <c r="B42" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C42" s="23">
         <f>SUM(C3:C41)</f>
-        <v>14870332</v>
+        <v>14982875</v>
       </c>
       <c r="D42" s="23">
         <f t="shared" ref="D42:J42" si="1">SUM(D3:D41)</f>
-        <v>1355180</v>
+        <v>1343676</v>
       </c>
       <c r="E42" s="23">
         <f t="shared" si="1"/>
-        <v>27115</v>
+        <v>27319</v>
       </c>
       <c r="F42" s="23">
         <f t="shared" si="1"/>
-        <v>982</v>
+        <v>1314</v>
       </c>
       <c r="G42" s="23">
         <f t="shared" si="1"/>
-        <v>24494</v>
+        <v>24595</v>
       </c>
       <c r="H42" s="23">
         <f t="shared" si="1"/>
-        <v>433198</v>
+        <v>435435</v>
       </c>
       <c r="I42" s="23">
         <f>SUM(I3:I41)</f>
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J42" s="23">
         <f t="shared" si="1"/>
-        <v>917</v>
+        <v>948</v>
       </c>
       <c r="K42" s="23">
         <f>SUM(K3:K41)</f>
-        <v>2384</v>
+        <v>2405</v>
       </c>
       <c r="L42" s="23">
         <f>SUM(L3:L41)</f>
-        <v>16712262</v>
+        <v>16816203</v>
       </c>
       <c r="M42" s="9"/>
     </row>
@@ -2740,17 +2740,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6AE321-CD75-4C1D-B892-B20887EA78E4}">
   <dimension ref="C1:H31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="54.5546875" customWidth="1"/>
-    <col min="4" max="4" width="24.88671875" customWidth="1"/>
+    <col min="3" max="3" width="54.54296875" customWidth="1"/>
+    <col min="4" max="4" width="24.90625" customWidth="1"/>
     <col min="5" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="16.88671875" customWidth="1"/>
+    <col min="7" max="7" width="16.90625" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C2" s="26" t="s">
         <v>51</v>
       </c>
@@ -2760,7 +2760,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="28"/>
     </row>
-    <row r="3" spans="3:8" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:8" ht="46.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C3" s="22" t="s">
         <v>52</v>
       </c>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="H3" s="30"/>
     </row>
-    <row r="4" spans="3:8" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:8" ht="15.5" x14ac:dyDescent="0.35">
       <c r="C4" s="15" t="s">
         <v>53</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C5" s="17" t="s">
         <v>59</v>
       </c>
@@ -2816,7 +2816,7 @@
         <v>2.2575679835813236E-2</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C6" s="17" t="s">
         <v>60</v>
       </c>
@@ -2836,7 +2836,7 @@
         <v>5.6962025316455694E-2</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C7" s="17" t="s">
         <v>61</v>
       </c>
@@ -2856,7 +2856,7 @@
         <v>5.2291164218373166E-3</v>
       </c>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C8" s="17" t="s">
         <v>62</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>5.2765738052777282E-2</v>
       </c>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C9" s="17" t="s">
         <v>63</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>0.18609019136111815</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C10" s="17" t="s">
         <v>64</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>1.6750902527075812E-2</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C11" s="17" t="s">
         <v>65</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>5.4263565891472867E-2</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C12" s="17" t="s">
         <v>66</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>4.7886204458299567E-2</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C13" s="17" t="s">
         <v>67</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>5.1009997959600086E-4</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C14" s="17" t="s">
         <v>68</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>7.2553831905533689E-2</v>
       </c>
     </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C15" s="17" t="s">
         <v>69</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>8.337359031167231E-3</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C16" s="17" t="s">
         <v>70</v>
       </c>
@@ -3036,7 +3036,7 @@
         <v>8.4881483386391648E-2</v>
       </c>
     </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C17" s="17" t="s">
         <v>71</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>1.6028309741881765E-2</v>
       </c>
     </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C18" s="17" t="s">
         <v>72</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>1.1477151965993623E-2</v>
       </c>
     </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C19" s="17" t="s">
         <v>73</v>
       </c>
@@ -3096,7 +3096,7 @@
         <v>4.8347035478933523E-3</v>
       </c>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C20" s="17" t="s">
         <v>74</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>8.4904696855570727E-2</v>
       </c>
     </row>
-    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C21" s="24" t="s">
         <v>7</v>
       </c>
@@ -3136,44 +3136,44 @@
         <v>0.15436773596949313</v>
       </c>
     </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C23" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C24" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C25" s="14" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="26" spans="3:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C26" s="31" t="s">
         <v>78</v>
       </c>
       <c r="D26" s="32"/>
     </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C27" s="33"/>
       <c r="D27" s="34"/>
     </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C28" s="33"/>
       <c r="D28" s="34"/>
     </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C29" s="33"/>
       <c r="D29" s="34"/>
     </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:8" x14ac:dyDescent="0.35">
       <c r="C30" s="33"/>
       <c r="D30" s="34"/>
     </row>
-    <row r="31" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C31" s="35"/>
       <c r="D31" s="36"/>
     </row>
@@ -3186,4 +3186,10 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a0819fa7-4367-4500-ba88-dd630d977609}" enabled="1" method="Standard" siteId="{63ce7d59-2f3e-42cd-a8cc-be764cff5eb6}" removed="0"/>
+</clbl:labelList>
 </file>